--- a/artfynd/A 25671-2026 artfynd.xlsx
+++ b/artfynd/A 25671-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>133856856</v>
       </c>
       <c r="B8" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25671-2026 artfynd.xlsx
+++ b/artfynd/A 25671-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>133856856</v>
       </c>
       <c r="B8" t="n">
-        <v>79977</v>
+        <v>79978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25671-2026 artfynd.xlsx
+++ b/artfynd/A 25671-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>133856856</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25671-2026 artfynd.xlsx
+++ b/artfynd/A 25671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129145381</v>
+        <v>130153769</v>
       </c>
       <c r="B2" t="n">
-        <v>92899</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N. Acksjön, Srm</t>
+          <t>N Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636882</v>
+        <v>636875</v>
       </c>
       <c r="R2" t="n">
-        <v>6554141</v>
+        <v>6554136</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129145374</v>
+        <v>129145388</v>
       </c>
       <c r="B3" t="n">
-        <v>97627</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>N. Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636888</v>
+        <v>636973</v>
       </c>
       <c r="R3" t="n">
-        <v>6554183</v>
+        <v>6554236</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -875,49 +870,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129145377</v>
+        <v>129145381</v>
       </c>
       <c r="B4" t="n">
-        <v>97627</v>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>N. Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636925</v>
+        <v>636882</v>
       </c>
       <c r="R4" t="n">
-        <v>6554225</v>
+        <v>6554141</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -977,10 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129145371</v>
+        <v>129145369</v>
       </c>
       <c r="B5" t="n">
-        <v>79689</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636963</v>
+        <v>636973</v>
       </c>
       <c r="R5" t="n">
-        <v>6554184</v>
+        <v>6554236</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1074,45 +1065,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129986214</v>
+        <v>129145370</v>
       </c>
       <c r="B6" t="n">
-        <v>101109</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Acksjön, Srm</t>
+          <t>N. Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636885</v>
+        <v>637003</v>
       </c>
       <c r="R6" t="n">
-        <v>6554147</v>
+        <v>6554165</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,12 +1130,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,10 +1162,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130153769</v>
+        <v>129145371</v>
       </c>
       <c r="B7" t="n">
-        <v>97197</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,34 +1173,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Acksjön, Srm</t>
+          <t>N. Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636875</v>
+        <v>636963</v>
       </c>
       <c r="R7" t="n">
-        <v>6554136</v>
+        <v>6554184</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,12 +1227,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,7 +1262,7 @@
         <v>133856856</v>
       </c>
       <c r="B8" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,6 +1362,536 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129972588</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>N Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6554172</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114458262</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Acksjön, Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>636976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6554106</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-01-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-01-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tupp och höna stöttes från träd. Mycket spillning på snön under tallarna. Även färsk blindtarmstömning mitt på sörmlandsleden.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129145374</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N. Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>636888</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6554183</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129145377</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N. Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>636925</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6554225</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129986214</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>636885</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6554147</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25671-2026 artfynd.xlsx
+++ b/artfynd/A 25671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130153769</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145381</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145369</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856856</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,8 +1952,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>